--- a/artfynd/A 3566-2024 artfynd.xlsx
+++ b/artfynd/A 3566-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3566-2024 artfynd.xlsx
+++ b/artfynd/A 3566-2024 artfynd.xlsx
@@ -675,44 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114567374</v>
+        <v>114571557</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1106</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Munga-Horndal, Vstm</t>
@@ -722,7 +713,7 @@
         <v>583315</v>
       </c>
       <c r="R2" t="n">
-        <v>6650784</v>
+        <v>6650782</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,61 +765,52 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mårten Nilsson, Louise Almén</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114567376</v>
+        <v>114571558</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583295</v>
+        <v>583318</v>
       </c>
       <c r="R3" t="n">
-        <v>6650705</v>
+        <v>6650783</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,49 +862,44 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mårten Nilsson, Louise Almén</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114567377</v>
+        <v>114567375</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583389</v>
+        <v>583270</v>
       </c>
       <c r="R4" t="n">
-        <v>6650730</v>
+        <v>6650694</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114571557</v>
+        <v>114567373</v>
       </c>
       <c r="B5" t="n">
-        <v>90532</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1106</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583315</v>
+        <v>583343</v>
       </c>
       <c r="R5" t="n">
-        <v>6650782</v>
+        <v>6650797</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,57 +1060,56 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Louise Almén</t>
+          <t>Mårten Nilsson, Louise Almén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114571558</v>
+        <v>114567374</v>
       </c>
       <c r="B6" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583318</v>
+        <v>583315</v>
       </c>
       <c r="R6" t="n">
-        <v>6650783</v>
+        <v>6650784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,49 +1161,44 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Almén</t>
+          <t>Mårten Nilsson, Louise Almén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114567375</v>
+        <v>114567376</v>
       </c>
       <c r="B7" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1241,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583270</v>
+        <v>583295</v>
       </c>
       <c r="R7" t="n">
-        <v>6650694</v>
+        <v>6650705</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,50 +1269,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114567378</v>
+        <v>114567377</v>
       </c>
       <c r="B8" t="n">
-        <v>96613</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583460</v>
+        <v>583389</v>
       </c>
       <c r="R8" t="n">
-        <v>6650694</v>
+        <v>6650730</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,15 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114567373</v>
+        <v>114967878</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,20 +1398,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Munga-Horndal, Vstm</t>
+          <t>Broddbo SO, ca 350 m ONO om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583343</v>
+        <v>583315</v>
       </c>
       <c r="R9" t="n">
-        <v>6650797</v>
+        <v>6650783</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1473,6 +1445,11 @@
           <t>Sala socken</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>U-Sal-0848</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>2023-06-04</t>
@@ -1483,19 +1460,25 @@
           <t>2023-06-04</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>(minst 11 ex) X: (10), 10 ex, A. 435/086 (10) not FV egentligen (32)</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mårten Nilsson</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -1503,69 +1486,56 @@
           <t>Mårten Nilsson, Louise Almén</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige, Inventering längs blivande kraftledning Munga-Horndal</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114967878</v>
+        <v>114567378</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Broddbo SO, ca 350 m ONO om (knärot), Vstm</t>
+          <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583315</v>
+        <v>583460</v>
       </c>
       <c r="R10" t="n">
-        <v>6650783</v>
+        <v>6650694</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1587,11 +1557,6 @@
           <t>Sala socken</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>U-Sal-0848</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
           <t>2023-06-04</t>
@@ -1602,25 +1567,19 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>(minst 11 ex) X: (10), 10 ex, A. 435/086 (10) not FV egentligen (32)</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Mårten Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -1628,11 +1587,7 @@
           <t>Mårten Nilsson, Louise Almén</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige, Inventering längs blivande kraftledning Munga-Horndal</t>
-        </is>
-      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3566-2024 artfynd.xlsx
+++ b/artfynd/A 3566-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114571557</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114571558</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567375</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567373</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567374</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567376</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567377</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
           <t>Floraväkteri Sverige, Inventering längs blivande kraftledning Munga-Horndal</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114967878</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1588,8 +1633,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567378</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>